--- a/important_mails_2026-03-30.xlsx
+++ b/important_mails_2026-03-30.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H156"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
+          <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -510,11 +510,63 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to reactivate listings</t>
+          <t>Your payment is on the way</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 03/30/26 15:13 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
+ 133.79.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -532,40 +584,93 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Dein Einkaufswagen wartet</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
+Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
+ 18,45 €
+https://www.amazon.de/gp/product/B0DRC8LPGS/?ref_=
+Einkaufswagen anzeigen
+https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schaue dir weitere Optionen an
+WOCVRYY130x160cm BBQ-Bodenschutzmatte Feuerschalenmatte Gasgrillmatte Unter Fireproof Underlay Wiederverwendbar,Antihaft-Material,Anti-Fall,Leicht zu reinigen und wasserdicht
+ 22,99 €
+https://www.amazon.de/gp/product/B0CQNQ2YY3/?ref_=ci_mcx_mr_2p_0_lm
+Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
+ 20,15 €
+https://www.amazon.de/gp/product/B0CSGBZG8W/?ref_=ci_mcx_mr_2p_1_lm
+Weber Grillmatte - Klein (120 x 80cm), schützt Terasse/Balkon vor Fettspritzern oder tropfenden Flüssigkeiten, hitze- &amp;amp; witterungsbeständiges antibakteriellles Material, für alle Grills (17897)
+ -19 % 25,20 € UVP: 31,08 €
+https://www.amazon.de/gp/product/B07ZCJHJQK/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -581,39 +686,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -633,39 +738,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -691,39 +796,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -740,39 +845,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -790,39 +895,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -840,39 +945,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -887,39 +992,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -937,39 +1042,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -987,39 +1092,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1037,39 +1142,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -1084,39 +1189,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -1131,39 +1236,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -1178,39 +1283,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1229,91 +1334,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Submit UK import details by 21/05/2026 to avoid shipping
- restrictions</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit UK import details by 21/05/2026 to avoid shipping restrictions
- Hello Weihai EU,
- Your Amazon.co.uk seller account requires Import Entry Numbers (IENs) for shipments to UK fulfilment centres. You must provide these details by 21/05/2026 to continue creating new UK shipments.
- Why is this happening?
- We are taking this action because we identified shipments to Amazon UK fulfilment centres without valid Import Entry Numbers (IENs). UK Customs authorities assign these IENs when goods are imported into the UK. As the seller, you must obtain these numbers from your customs declarant, logistics agent or freight forwarder to maintain UK shipping compliance .
- Where do I enter my Import Entry Numbers (IEN)?
- To enter the IENs for your applicable shipments:
-- Go to your Shipping Queue and identify shipments received in Amazon UK FCs.
-- Under “Status”, click the “Import details” text. It will open a pop-up, where you can enter the IENs corresponding to the relevant shipment. You must provide a valid IEN.
-- Save your IEN entry.
- If you would need to update your IEN, you can follow the above steps again.
- What happens if I don’t submit these details?
- You have 60 days after first re</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1328,39 +1381,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -1374,40 +1427,40 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -1423,39 +1476,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -1471,39 +1524,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -1519,39 +1572,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -1567,40 +1620,40 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -1616,39 +1669,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -1666,39 +1719,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -1714,39 +1767,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1761,39 +1814,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -1808,39 +1861,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1861,40 +1914,40 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -1909,39 +1962,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1962,39 +2015,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2017,39 +2070,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -2065,39 +2118,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2113,39 +2166,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2166,39 +2219,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -2212,40 +2265,40 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -2261,39 +2314,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2313,39 +2366,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -2359,39 +2412,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2411,39 +2464,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2464,39 +2517,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2516,39 +2569,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 20:32:33 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (DjHMcVqBnq)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2568,39 +2621,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2617,39 +2670,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -2664,39 +2717,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2720,39 +2773,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2766,39 +2819,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2815,39 +2868,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2867,39 +2920,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 15:38:46 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2916,39 +2969,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 16:06:24 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2972,39 +3025,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 14:48:41 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -3024,39 +3077,91 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Submit UK import details by 21/05/2026 to avoid shipping
+ restrictions</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit UK import details by 21/05/2026 to avoid shipping restrictions
+ Hello Weihai EU,
+ Your Amazon.co.uk seller account requires Import Entry Numbers (IENs) for shipments to UK fulfilment centres. You must provide these details by 21/05/2026 to continue creating new UK shipments.
+ Why is this happening?
+ We are taking this action because we identified shipments to Amazon UK fulfilment centres without valid Import Entry Numbers (IENs). UK Customs authorities assign these IENs when goods are imported into the UK. As the seller, you must obtain these numbers from your customs declarant, logistics agent or freight forwarder to maintain UK shipping compliance .
+ Where do I enter my Import Entry Numbers (IEN)?
+ To enter the IENs for your applicable shipments:
+- Go to your Shipping Queue and identify shipments received in Amazon UK FCs.
+- Under “Status”, click the “Import details” text. It will open a pop-up, where you can enter the IENs corresponding to the relevant shipment. You must provide a valid IEN.
+- Save your IEN entry.
+ If you would need to update your IEN, you can follow the above steps again.
+ What happens if I don’t submit these details?
+ You have 60 days after first re</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3066,39 +3171,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3116,39 +3221,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -3164,39 +3269,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3215,39 +3320,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3265,39 +3370,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -3319,39 +3424,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -3374,39 +3479,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3425,39 +3530,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3476,39 +3581,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3528,39 +3633,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3580,39 +3685,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -3630,39 +3735,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3680,39 +3785,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Rispondi ai requisiti di conformità per le tue offerte</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 Azione richiesta: Informazioni importanti sulle sue offerte
@@ -3730,39 +3835,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3781,89 +3886,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Feb 2026 05:28:30 +0000</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Hantera efterlevnadskrav för dina produktposter</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>96
-Åtgärd krävs: Viktig information angående dina produktposter
- Vi kontaktar dig eftersom du har publicerat produkter som du måste skicka in dokument om överensstämmelse för.
- Produktposterna saknar dokument om överensstämmelse
- Hej!
- Vi kontaktar dig eftersom du har publicerat produkter för vilka du måste skicka in dokument om överensstämmelse. Klicka på Granska krav på överensstämmelse nedan om du vill visa listan med berörda produkter och skicka sedan in de dokument om överensstämmelse som krävs. Om du inte skickar in dokumenten senast det angivna förfallodatumet för respektive produkt i den här länken, så kan vi komma att ta bort de berörda produktposterna.
- Visa krav på överensstämmelse
- I tabellen nedan visas en av dina berörda produktposter som exempel. Klicka på Granska krav på överensstämmelse om du vill se alla dina berörda produktposter.
- SKU ASIN Status K6-KGRL-T8E4 B0DYTPRM8Z Riskerar borttagning
- Varför händer det här?
-Det här kravet hjälper till att säkerställa att produkterna är säkra för kunderna och överensstämmer med lokala lagar.
- Vad behöver jag göra om jag vill fortsätta att sälja de här produkterna?
-Klicka på Granska krav på överensstämmelse om du vill ha me</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -3884,39 +3939,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -3949,39 +4004,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -3997,39 +4052,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4045,39 +4100,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4095,39 +4150,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4144,39 +4199,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -4200,39 +4255,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4247,39 +4302,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -4295,39 +4350,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4344,40 +4399,40 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -4393,39 +4448,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4445,39 +4500,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4493,40 +4548,40 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4542,39 +4597,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4591,39 +4646,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4642,39 +4697,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4692,39 +4747,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -4736,39 +4791,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4780,39 +4835,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -4824,39 +4879,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4868,39 +4923,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4912,39 +4967,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -4956,39 +5011,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5000,39 +5055,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5044,39 +5099,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -5094,39 +5149,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -5169,39 +5224,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5218,40 +5273,40 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5269,39 +5324,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5319,39 +5374,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5363,39 +5418,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5407,39 +5462,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5458,39 +5513,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5502,39 +5557,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5546,39 +5601,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5590,39 +5645,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5634,39 +5689,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5678,39 +5733,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5722,39 +5777,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5766,39 +5821,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5810,39 +5865,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5854,40 +5909,40 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5906,39 +5961,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5950,40 +6005,40 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -5995,39 +6050,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6039,39 +6094,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6090,39 +6145,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6134,39 +6189,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6185,39 +6240,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -6229,39 +6284,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6277,40 +6332,40 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6328,39 +6383,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6378,39 +6433,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -6426,39 +6481,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -6476,39 +6531,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -6549,39 +6604,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6599,40 +6654,40 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6650,39 +6705,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6699,39 +6754,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6749,39 +6804,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6799,39 +6854,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>最后机会：请在3月9日前提报春季促销日的促销</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>3月9日前提报春季促销日促销
 尊敬的卖家，
@@ -6846,39 +6901,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6892,58 +6947,10 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Feb 2026 11:10:30 +0000</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>Worten Marketplace - Portugal y España</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>¡Buenos días!
-Espero que te encuentres bien.
-Mi nombre es Gabriel Martins y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
-Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
-Sobre Worten.
-Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
-En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
-Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
-Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
-Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
-Worten Marketplace tiene una estrategia B2C,</t>
-        </is>
-      </c>
-    </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6958,228 +6965,21 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Sat, 28 Feb 2026 02:13:10 +0000</t>
+          <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>[Toma medidas] Proporciona más información en un plazo de 60 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
+          <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Hola, Weihai EU:
- Para cumplir nuestros requisitos de registro del impuesto sobre el valor añadido (IVA) europeo, necesitamos que nos proporciones más información.
- ¿A qué se debe esto?
- De acuerdo con nuestros requisitos de registro a efectos fiscales en Europa, tienes que proporcionarnos un número de identificación fiscal válido de todos los países en los que consideremos que tienes obligación de registrarte a efectos fiscales o confirmar el estado de registro en la Ventanilla Única del IVA (OSS) en tu país de origen.
- Hemos detectado que tu cuenta tiene que cumplir una serie de requisitos para el registro a efectos fiscales en la Unión Europea, el Reino Unido, Noruega y Suiza, donde tienes la obligación de registrarte a efectos fiscales. En concreto, es posible que tengas que tomar medidas para lo siguiente:
- Polonia
- Para más información, consulta Información sobre el impuesto sobre el valor añadido (IVA) europeo .
- ¿Cómo evito la desactivación de mi cuenta?
- Para evitar la desactivación de la cuenta, consulta la sección "Acciones prioritarias" de la página Estado de la cuenta en los próximos 60 días. Desde ahí podrás hacer lo siguiente:
-- Revisar la información que tienes </t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Feb 2026 02:09:55 +0000</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 60 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>96
- Dzień dobry Weihai EU,
- potrzebujemy od Ciebie dodatkowych informacji, które pozwolą Ci spełnić europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT.
- Dlaczego tak się stało?
- Zgodnie z europejskimi wymaganiami Amazon dotyczącymi rejestracji jako podatnik VAT musisz podać nam ważny numer VAT dla wszystkich krajów, w których według nas podlegasz obowiązkowi rejestracji jako podatnik VAT, lub potwierdzenie statusu rejestracji w procedurze unijnej w Twoim kraju macierzystym.
- Ustaliliśmy, że w przypadku Twojego konta w Unii Europejskiej, Zjednoczonym Królestwie, Norwegii i Szwajcarii, gdzie masz zobowiązania z tytułu VAT, istnieją wymogi w zakresie rejestracji jako podatnik VAT. Podjęcie działań może być w szczególności wymagane w następujących przypadkach:
- Polska
- Więcej informacji znajdziesz na stronie Informacje dotyczące podatku VAT w Europie .
- Jak mogę zapobiec dezaktywacji konta?
- Aby uniknąć dezaktywacji konta, w ciągu najbliższych 60 dni odwiedź sekcję „Działania priorytetowe” na stronie Kondycja konta . W sekcji tej można:
-- zweryfikować istniejące informacje dotyczące wymienionych krajów
-- przesłać informacje o VAT za pośrednictwem portali „Informacje o</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Feb 2026 02:07:47 +0000</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>[Azione richiesta] Fornisci informazioni entro 60 giorni ed evita
- la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>96
- Gentile Weihai EU,
- Ai fini della conformità ai requisiti di registrazione IVA in Europa di Amazon, ti chiediamo di fornirci ulteriori informazioni.
- Ciò a cosa è dovuto?
- In base ai requisiti di registrazione IVA in Europa di Amazon, sei tenuto a fornirci un numero di partita IVA valido per tutti i paesi in cui riteniamo che tu abbia l'obbligo di effettuare tale registrazione o una conferma dello stato Union One-Stop Shop (OSS) relativo al tuo paese di registrazione.
- Vi sono dei requisiti per la registrazione ai fini IVA che il tuo account deve soddisfare nei paesi in cui sei soggetto a obblighi in materia di IVA (stati dell'Unione europea, Regno Unito, Norvegia e Svizzera). Nello specifico, potrebbe essere necessario un intervento da parte tua per quanto segue:
- Polonia
- Per maggiori informazioni, consulta la pagina di aiuto Informazioni sull'IVA in Europa .
- Come faccio a evitare la disattivazione dell'account?
- Per evitare la disattivazione dell'account, visita entro i prossimi 60 giorni la sezione relativa alle azioni prioritarie della pagina Stato dell'account . Da qui, potrai effettuare le seguenti operazioni:
-- Verificare le informazioni esistenti per i paesi in elenco</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Feb 2026 18:30:15 +0000</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>Tus límites de capacidad de Logística de Amazon para marzo</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>96
- Tus límites de capacidad de Logística de Amazon para marzo
- Hola:
- Se confirmaron tus límites de capacidad para el próximo periodo.
- Pronóstico de capacidad para el periodo del mar. 1 al 31, a partir del feb. 26:
- Tipo de almacenamiento
- Límite de capacidad total (metros cúbicos)
- Tamaño estándar
- 16.42
- Tamaño grande
- 21.66
- Para ver tus límites más actualizados, así como los límites de capacidad estimados para los dos meses siguientes, ve a los envíos de Logística de Amazon .
- En la siguiente tabla, se muestra el uso de la capacidad de Logística de Amazon a partir del feb. 25.
- Tipo de almacenamiento
- Uso sin los envíos abiertos incluidos (metros cúbicos)
- Uso con los envíos abiertos incluidos (metros cúbicos)
- Tamaño estándar
- 0.00
- 0.00
- Tamaño grande
- 0.00
- 0.00
- Cómo se establecen los límites de capacidad de Logística de Amazon
- Tus límites de capacidad dependen de tu puntuación del índice de desempeño de inventario y otros factores, como las proyecciones de ventas para tus ASIN, la capacidad del centro de distribución y el plazo de entrega de los envíos. Las estimaciones variarán en función de los cambios en tu puntuación del índice de desempeño de inventario y pueden au</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-02</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7200,39 +7000,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7256,39 +7056,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7311,39 +7111,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7366,39 +7166,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7420,39 +7220,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7475,39 +7275,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7530,39 +7330,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -7588,39 +7388,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7636,40 +7436,40 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7688,40 +7488,40 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7739,39 +7539,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -7785,39 +7585,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -7835,39 +7635,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -7884,39 +7684,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -7934,40 +7734,40 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -7986,39 +7786,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
@@ -8034,39 +7834,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>View your US Q1-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q1-2026
@@ -8096,109 +7896,6 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Feb 2026 02:10:48 +0000</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>[Action Required] Provide additional information within 60 days to
- avoid account deactivation under European VAT registration requirements</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai EU,
- We need you to provide additional information in order to comply with Amazon’s European Value Added Tax (VAT) registration requirements.
- Why is this happening?
- According to Amazon’s European VAT registration requirements you must provide us with a valid VAT Registration Number (‘VRN’) for all the countries in which we believe you have a VAT registration obligation or confirmation of the Union One-Stop Shop (OSS) status for your home country.
- We identified VAT registration requirements for your account in the European Union, the United Kingdom, Norway, and Switzerland in which you have VAT obligation. Specifically, action may be required for the following:
- Poland
- To learn more, go to the European Value Added Tax Information Help page.
- How do I avoid account deactivation?
- To avoid account deactivation, within the next 60 days visit the Priority Actions section on your Account Health page . From there, you will be able to:
-- Verify your existing information for listed countries
-- Submit VAT information through Business Information and Tax Setting portals
-- Submit required documentation for extension or exemption requests
- What happens if I don’t provide th</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Feb 2026 02:06:07 +0000</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>[Action required] Provide additional information within 60 days to
- avoid account deactivation under European VAT registration requirements</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai EU,
- We need you to provide additional information in order to comply with Amazon’s European Value Added Tax (VAT) registration requirements.
- Why is this happening?
- According to Amazon’s European VAT registration requirements, you must provide us with a valid VAT registration number (“VRN”) for all the countries in which we believe you have a VAT registration obligation, or confirmation of the Union One-Stop Shop (OSS) status for your home country.
- We identified VAT registration requirements for your account in the European Union, the United Kingdom, Norway and Switzerland in which you have Value Added Tax (VAT) obligation. Specifically, action may be required for the following:
- Poland
- To learn more, go to the European Value Added Tax information help page.
- How do I avoid account deactivation?
- To avoid account deactivation, within the next 60 days visit the Priority actions section on your Account Health page . From there, you will be able to:
-- Verify your existing information for listed countries
-- Submit Value Added Tax (VAT) information through business information and tax setting portals
-- Submit required documentation for extension or exemption request</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/important_mails_2026-03-30.xlsx
+++ b/important_mails_2026-03-30.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -602,21 +602,82 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
+          <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+          <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Dein Einkaufswagen wartet</t>
+          <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Tus límites de capacidad de Logística de Amazon para abril
+ Hola:
+ Se confirmaron tus límites de capacidad para el próximo periodo.
+ Pronóstico de capacidad para el periodo del abr. 1 al 30, a partir del mar. 28:
+ Tipo de almacenamiento
+ Límite de capacidad total (metros cúbicos)
+ Tamaño estándar
+ 16.42
+ Tamaño grande
+ 21.66
+ Para ver tus límites más actualizados, así como los límites de capacidad estimados para los dos meses siguientes, ve a los envíos de Logística de Amazon .
+ En la siguiente tabla, se muestra el uso de la capacidad de Logística de Amazon a partir del mar. 27.
+ Tipo de almacenamiento
+ Uso sin los envíos abiertos incluidos (metros cúbicos)
+ Uso con los envíos abiertos incluidos (metros cúbicos)
+ Tamaño estándar
+ 0.00
+ 0.00
+ Tamaño grande
+ 0.00
+ 0.00
+ Cómo se establecen los límites de capacidad de Logística de Amazon
+ Tus límites de capacidad dependen de tu puntuación del índice de desempeño de inventario y otros factores, como las proyecciones de ventas para tus ASIN, la capacidad del centro de distribución y el plazo de entrega de los envíos. Las estimaciones variarán en función de los cambios en tu puntuación del índice de desempeño de inventario y pueden au</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Dein Einkaufswagen wartet</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -637,40 +698,40 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -686,39 +747,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -738,39 +799,1313 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>View your China tax report for October - December 2025</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96
+ We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
+ Hello,
+ According to rules for online stores issued by the State Council of China (Decree No. 810), we are required to provide information on China-based sellers to the Chinese tax authority on a quarterly basis.
+ We’ve submitted your quarterly tax report covering October to December 2025, which includes your identity information, number of transactions, revenue, and commission and service fees.
+ Download your quarterly report (link active for seven days)
+This report is provided for your reference only, no action is required.
+ Based on your feedback, we’ve also provided a more granular order-level report that displays your quarterly information by transaction.
+ Download your order-level report (link active for seven days)
+Note: Variation between the data in these reports and your payment and Amazon VAT transactions report is expected. Each report uses distinct methodology and serves a different purpose.
+ We’ll continue to provide you with quarterly updates on data shared with the Chinese tax authority.
+ For more information, go to China tax information reporti</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai CA,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Live Q&amp;A on customer feedback with experienced sellers</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
+Connect with sellers experienced in customer feedback
+Join us on March 31 for a live Q&amp;A event in the New Seller Community. Experienced Amazon selling partners will answer your customer feedback questions, offering insights from their own journey.
+Before the event, post your toughest questions about managing feedback, buyer-seller messaging, and customer relations.
+[Post your question](https://go.amazonsellerservices.com/e/229492/71-ref--spc-em-na-frm-20260324/7z2bw3v/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
+[An Amazon delivery driver walks next to an Amazon Prime delivery van.](https://go.amazonsellerservices.com/e/229492/71-ref--spc-em-na-frm-20260324/7z2bw3v/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
+Meet our hosts
+[A checkmark icon]
+Amazon Seller: TVOI50
+Hi, my name is Tish. We’ve been selling on Amazon for 5 years in the Office Furniture category. We are FBM, an authorized re-seller for a major furniture manufacturer and strive to make every transaction a seamless one. If it’s not, our customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai CA,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Action Required: Website Suppressed ASINs</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
+We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
+Here is a sample of your suppressed ASINs:
+B0FCDRNTT8, B0D7SKQ6GC
+You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
+https://sellercentral.amazon.com/fixyourproducts/drafts
+To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
+https://sellercentral.amazon.com/performance/account/health/compliance-request
+If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Action Required: Website Suppressed ASINs</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
+We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
+Here is a sample of your suppressed ASINs:
+B0D7SKQ6GC, B0FCDRNTT8
+You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
+https://sellercentral.amazon.com/fixyourproducts/drafts
+To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
+https://sellercentral.amazon.com/performance/account/health/compliance-request
+If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Action Required: Website Suppressed ASINs</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
+We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
+Here is a sample of your suppressed ASINs:
+B0D7SKQ6GC, B0FCDRNTT8
+You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
+https://sellercentral.amazon.com/fixyourproducts/drafts
+To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
+https://sellercentral.amazon.com/performance/account/health/compliance-request
+If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.com Inventory - Action Required</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Dear Weihai US,
+We have recently restricted listings for the product(s) listed below on Amazon.com.
+Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 04/20/2026), we may dispose of it in accordance with FBA policies.
+Thank you for your attention to this matter.
+Regards,
+Product Safety Team
+Amazon.com
+www.amazon.com
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0FD8VC559
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
+SPC-USAmazon-1161086478880000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Pagamento elaborato con successo</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
+ Tentativo di pagamento
+Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
+In data 03/28/26 15:19 CET, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
+ 217,83.
+ Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
+ Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
+ Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che p</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
+ Dzień dobry Weihai EU,
+ niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
+ Dlaczego tak się stało?
+ Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
+ Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
+ Jak mogę ponownie aktywować oferty?
+ Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
+ le offerte</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
+ Ciò a cosa è dovuto?
+ Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
+ La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
+ Come faccio a riattivare le mie offerte?
+ Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
+-
+ Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
+ Hej Weihai EU!
+ Vissa av dina produktposter har inaktiverats på grund av att det saknas obligatorisk överensstämmelse för dina produkter. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
+ Varför händer det här?
+ Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer. Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
+ Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
+ Hur återaktiverar jag mina produktposter?
+ Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
+-
+ Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna. Vi återaktiverar endast produkter som u</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
+ Bonjour Weihai EU,
+ Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
+ Pourquoi cela se produit-il ?
+ Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
+ Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
+ Comment réactiver mes produits mis en vente ?
+ Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
+-
+ Si vous disposez des documents requis, suivez les instructio</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Presenta la documentación sobre seguridad del producto para reactivar los listings
+ Hola, Weihai EU:
+ Algunos de tus listings se han desactivado debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
+ ¿A qué se debe esto?
+ Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos . Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar una decisión.
+ En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
+ ¿Cómo puedo reactivar mis listings?
+ Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
+-
+ Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cum</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Dien productveiligheidsdocumentatie in om productvermeldingen
+ opnieuw te activeren</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
+ Hallo Weihai EU,
+ Sommige van je productvermeldingen zijn gedeactiveerd omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
+ Waarom gebeurt dit?
+ We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid. We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
+ De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
+ Hoe activeer ik mijn productvermeldingen opnieuw?
+ Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
+-
+ Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen. We zullen alleen </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Worten Marketplace - Portugal y España</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Hola Weihai EU,
+Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
+Nuestro equipo de análisis ha señalado que una asociación con usted sería una gran oportunidad para ambos.
+¿Estaría disponible para una reunión online esta semana?
+Acerca de Worten - Somos el líder del mercado portugués:
+- Nº 1 del comercio electrónico portugués
+- Sitio web con mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
+- Más de 200 tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
+- Plataforma de gestión: Mirakl (se puede integrar manualmente o vía API)
+- Sin costes iniciales - 6 meses
+Estaré encantado de ayudarle si tiene alguna pregunta.
+Muchas gracias,
+Saludos Cordiales</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
+ Dzień dobry,
+ zgodnie z zasadami dotyczącymi sklepów internetowych wydanymi przez Radę Państwa Chin (dekret nr 810) jesteśmy zobowiązani do przekazywania informacji o sprzedawcach z siedzibą w Chinach tamtejszemu organowi podatkowemu w cyklach kwartalnych.
+ Przesłaliśmy Twój kwartalny raport podatkowy za okres od października do grudnia 2025 r., który zawiera Twoje dane identyfikacyjne, liczbę transakcji, przychody oraz prowizje i opłaty za usługi.
+ Pobierz swój kwartalny raport (link aktywny przez siedem dni)
+Raport jest przeznaczony wyłącznie do wglądu, nie jest wymagane żadne działanie.
+ Na podstawie Twojej opinii udostępniliśmy też bardziej szczegółowy raport na poziomie zamówienia, który przedstawia informacje kwartalne z podziałem na transakcje.
+ Pobierz raport na poziomie zamówienia (link aktywny przez siedem dni)
+Uwaga: mogą wystąpić różnice między danymi w tych raportach a raportem o płatnościach i raportem Amazon o transakcjach podlegających VAT. Każdy raport korzysta z odrębnej metodologii i służy do innego celu.
+ Będziemy Ci nadal przekazywać kwartalne</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Votre paiement est en cours</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Félicitations ! Votre paiement est en cours et arrivera sous peu.
+ Tentative de versement
+Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
+Le 03/25/26 15:00 CET, nous avons effectué un virement d’un montant de €
+ 41.37 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
+ Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
+ Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
+ Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de pér</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>借助 Climate Pledge Friendly 推动业务增长</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>借助 Climate Pledge Friendly 推动业务增长
+尊敬的卖家，
+参与亚马逊 Climate Pledge Friendly 计划的商品，在获得资格后的第一年内，平均可实现超过 12% 的销售增长和 10% 的商品页面浏览量提升*。
+我们诚邀您加入 Climate Pledge Friendly（CPF），提升您更具可持续性的商品曝光度，同时助力业务增长。
+拥有认可的[可持续发展认证](https://go.amazonsellerservices.com/e/229492/92469229-Wk13-node-21221608011/7z2bhly/6571059691/h/eRCozJPc0P6D8HNBb3qP94H1ForkIsaCTky_5R89ARk)的商品，有机会获得 Climate Pledge Friendly 标识，从而在消费者中脱颖而出。
+[立即开始](https://go.amazonsellerservices.com/e/229492/229-Wk13-mons-sel-locale-zh-CN/7z2bhm2/6571059691/h/eRCozJPc0P6D8HNBb3qP94H1ForkIsaCTky_5R89ARk)
+[CPF banner](https://go.amazonsellerservices.com/e/229492/229-Wk13-mons-sel-locale-zh-CN/7z2bhm2/6571059691/h/eRCozJPc0P6D8HNBb3qP94H1ForkIsaCTky_5R89ARk)
+优先审核的 ASIN
+这些商品选自您的商品目录，可能是获得 Climate Pledge Friendly 认证的潜在候选。
+&lt;div style="padding: 0 20px; "&gt;&lt;table style="width:100%; border-collapse:collapse; text-align:center; font-family:Amazon Ember Display, Arial, sans-serif; border:2px solid #868D95; border-radius:10px 10px 0 0; overflow:hidden; "&gt;&lt;thead&gt;&lt;tr style="background-color:#dfdad5;"&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Dein Einkaufswagen wartet</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
+ -7 % 21,81 € UVP: 23,49 €
+https://www.amazon.de/gp/product/B0DRCC2H56/?ref_=
+Einkaufswagen anzeigen
+https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schaue dir weitere Optionen an
+Roaxkois Keramikmalset, Tassenmalset enthält Tassen, Pinsel, Farben und Anleitungen zum Bemalen, Keramik-Set für Zuhause, Bastelset für Erwachsene (Welle)
+ 26,01 €
+https://www.amazon.de/gp/product/B0FLJ9RS6S/?ref_=ci_mcx_mr_2p_0_lm
+Roaxkois Keramik Bemalen Set - Kreatives Keramik Bastelset mit Farben, Pinseln und Anleitungen, Perfektes Tassen Bemalen Set für individuelle Geschenke und Freizeitgestaltung
+ -11 % 20,97 € UVP: 23,49 €
+https://www.amazon.de/gp/product/B0FD8PWPNK/?ref_=ci_mcx_mr_2p_1_lm
+LEOSINYIN Keramik Bemalen Set, Tassen Bemalen Set, DIY Keramik Malset Kreatives Geschenk für Kinder &amp;amp; Erwachsene Enthält 2*Tassen, 2*Farbwanne, 4*Pinsel, 2 * 12 Farben und Anleitung
+Befristetes Angebot -37 % 18,99 € UVP: 29,99 €
+https://www.amazon.de/gp/product/B0FBXF765H/?re</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-04-09</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-04-09 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: X002A05YW5 Quantity: 2
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- CQhO1/+c38
+ Unsellable Products:
+- FNSKU: X002C14R1B Quantity: 1
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>[Action Required] – Update Inventory -FBA</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
+We recommend that you inbound additional inventory for your products immediately. To view the recommended replenishment quantity for these ASINs, go to “Restock inventory”:
+https://sellercentral.amazon.ca/restockinventory/recommendations
+Here is a sample of your high selling FBA ASINs, which are considered low in stock at the moment:
+B0DMFL5X12, B0D7QHCF8J
+You can download the full list of your ASIN at risk of out of stock at the following link:  https://www.sellercentral.amazon.ca/reportcentral/RestockReport/1
+For more information about Restock tool, you can visit this help page - https://sellercentral.amazon.ca/gp/help/G201634550
+If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
+If you are not the correct point of contact, please re-direct this report to the correct point of contact.
+If you wish to unsubscribe please REPLY ALL with the subject l</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -796,1328 +2131,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>View your China tax report for October - December 2025</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96
- We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
- Hello,
- According to rules for online stores issued by the State Council of China (Decree No. 810), we are required to provide information on China-based sellers to the Chinese tax authority on a quarterly basis.
- We’ve submitted your quarterly tax report covering October to December 2025, which includes your identity information, number of transactions, revenue, and commission and service fees.
- Download your quarterly report (link active for seven days)
-This report is provided for your reference only, no action is required.
- Based on your feedback, we’ve also provided a more granular order-level report that displays your quarterly information by transaction.
- Download your order-level report (link active for seven days)
-Note: Variation between the data in these reports and your payment and Amazon VAT transactions report is expected. Each report uses distinct methodology and serves a different purpose.
- We’ll continue to provide you with quarterly updates on data shared with the Chinese tax authority.
- For more information, go to China tax information reporti</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Submit product safety documentation to reactivate listings
- Hello Weihai CA,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Live Q&amp;A on customer feedback with experienced sellers</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
-Connect with sellers experienced in customer feedback
-Join us on March 31 for a live Q&amp;A event in the New Seller Community. Experienced Amazon selling partners will answer your customer feedback questions, offering insights from their own journey.
-Before the event, post your toughest questions about managing feedback, buyer-seller messaging, and customer relations.
-[Post your question](https://go.amazonsellerservices.com/e/229492/71-ref--spc-em-na-frm-20260324/7z2bw3v/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
-[An Amazon delivery driver walks next to an Amazon Prime delivery van.](https://go.amazonsellerservices.com/e/229492/71-ref--spc-em-na-frm-20260324/7z2bw3v/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
-Meet our hosts
-[A checkmark icon]
-Amazon Seller: TVOI50
-Hi, my name is Tish. We’ve been selling on Amazon for 5 years in the Office Furniture category. We are FBM, an authorized re-seller for a major furniture manufacturer and strive to make every transaction a seamless one. If it’s not, our customer</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Submit product safety documentation to reactivate listings
- Hello Weihai CA,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Action Required: Website Suppressed ASINs</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
-We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
-Here is a sample of your suppressed ASINs:
-B0FCDRNTT8, B0D7SKQ6GC
-You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
-https://sellercentral.amazon.com/fixyourproducts/drafts
-To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
-https://sellercentral.amazon.com/performance/account/health/compliance-request
-If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Action Required: Website Suppressed ASINs</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
-We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
-Here is a sample of your suppressed ASINs:
-B0D7SKQ6GC, B0FCDRNTT8
-You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
-https://sellercentral.amazon.com/fixyourproducts/drafts
-To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
-https://sellercentral.amazon.com/performance/account/health/compliance-request
-If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Action Required: Website Suppressed ASINs</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
-We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
-Here is a sample of your suppressed ASINs:
-B0D7SKQ6GC, B0FCDRNTT8
-You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
-https://sellercentral.amazon.com/fixyourproducts/drafts
-To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
-https://sellercentral.amazon.com/performance/account/health/compliance-request
-If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.com Inventory - Action Required</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Dear Weihai US,
-We have recently restricted listings for the product(s) listed below on Amazon.com.
-Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 04/20/2026), we may dispose of it in accordance with FBA policies.
-Thank you for your attention to this matter.
-Regards,
-Product Safety Team
-Amazon.com
-www.amazon.com
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0FD8VC559
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
-SPC-USAmazon-1161086478880000</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Pagamento elaborato con successo</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
- Tentativo di pagamento
-Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
-In data 03/28/26 15:19 CET, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
- 217,83.
- Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
- Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
- Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che p</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
- Dzień dobry Weihai EU,
- niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
- Dlaczego tak się stało?
- Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
- Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
- Jak mogę ponownie aktywować oferty?
- Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
- le offerte</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>96
- Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
- Gentile Weihai EU,
- Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
- Ciò a cosa è dovuto?
- Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
- La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
- Come faccio a riattivare le mie offerte?
- Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
--
- Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>96
- Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
- Hej Weihai EU!
- Vissa av dina produktposter har inaktiverats på grund av att det saknas obligatorisk överensstämmelse för dina produkter. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
- Varför händer det här?
- Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer. Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
- Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
- Hur återaktiverar jag mina produktposter?
- Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
--
- Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna. Vi återaktiverar endast produkter som u</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>96
- Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
- Bonjour Weihai EU,
- Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
- Pourquoi cela se produit-il ?
- Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
- Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
- Comment réactiver mes produits mis en vente ?
- Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
--
- Si vous disposez des documents requis, suivez les instructio</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>96
- Presenta la documentación sobre seguridad del producto para reactivar los listings
- Hola, Weihai EU:
- Algunos de tus listings se han desactivado debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
- ¿A qué se debe esto?
- Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos . Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar una decisión.
- En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
- ¿Cómo puedo reactivar mis listings?
- Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
--
- Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cum</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Dien productveiligheidsdocumentatie in om productvermeldingen
- opnieuw te activeren</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
- Hallo Weihai EU,
- Sommige van je productvermeldingen zijn gedeactiveerd omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
- Waarom gebeurt dit?
- We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid. We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
- De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
- Hoe activeer ik mijn productvermeldingen opnieuw?
- Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
--
- Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen. We zullen alleen </t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Worten Marketplace - Portugal y España</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Hola Weihai EU,
-Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
-Nuestro equipo de análisis ha señalado que una asociación con usted sería una gran oportunidad para ambos.
-¿Estaría disponible para una reunión online esta semana?
-Acerca de Worten - Somos el líder del mercado portugués:
-- Nº 1 del comercio electrónico portugués
-- Sitio web con mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
-- Más de 200 tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
-- Plataforma de gestión: Mirakl (se puede integrar manualmente o vía API)
-- Sin costes iniciales - 6 meses
-Estaré encantado de ayudarle si tiene alguna pregunta.
-Muchas gracias,
-Saludos Cordiales</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>96
- Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
- Dzień dobry,
- zgodnie z zasadami dotyczącymi sklepów internetowych wydanymi przez Radę Państwa Chin (dekret nr 810) jesteśmy zobowiązani do przekazywania informacji o sprzedawcach z siedzibą w Chinach tamtejszemu organowi podatkowemu w cyklach kwartalnych.
- Przesłaliśmy Twój kwartalny raport podatkowy za okres od października do grudnia 2025 r., który zawiera Twoje dane identyfikacyjne, liczbę transakcji, przychody oraz prowizje i opłaty za usługi.
- Pobierz swój kwartalny raport (link aktywny przez siedem dni)
-Raport jest przeznaczony wyłącznie do wglądu, nie jest wymagane żadne działanie.
- Na podstawie Twojej opinii udostępniliśmy też bardziej szczegółowy raport na poziomie zamówienia, który przedstawia informacje kwartalne z podziałem na transakcje.
- Pobierz raport na poziomie zamówienia (link aktywny przez siedem dni)
-Uwaga: mogą wystąpić różnice między danymi w tych raportach a raportem o płatnościach i raportem Amazon o transakcjach podlegających VAT. Każdy raport korzysta z odrębnej metodologii i służy do innego celu.
- Będziemy Ci nadal przekazywać kwartalne</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Votre paiement est en cours</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Félicitations ! Votre paiement est en cours et arrivera sous peu.
- Tentative de versement
-Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
-Le 03/25/26 15:00 CET, nous avons effectué un virement d’un montant de €
- 41.37 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
- Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
- Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
- Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de pér</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>借助 Climate Pledge Friendly 推动业务增长</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>借助 Climate Pledge Friendly 推动业务增长
-尊敬的卖家，
-参与亚马逊 Climate Pledge Friendly 计划的商品，在获得资格后的第一年内，平均可实现超过 12% 的销售增长和 10% 的商品页面浏览量提升*。
-我们诚邀您加入 Climate Pledge Friendly（CPF），提升您更具可持续性的商品曝光度，同时助力业务增长。
-拥有认可的[可持续发展认证](https://go.amazonsellerservices.com/e/229492/92469229-Wk13-node-21221608011/7z2bhly/6571059691/h/eRCozJPc0P6D8HNBb3qP94H1ForkIsaCTky_5R89ARk)的商品，有机会获得 Climate Pledge Friendly 标识，从而在消费者中脱颖而出。
-[立即开始](https://go.amazonsellerservices.com/e/229492/229-Wk13-mons-sel-locale-zh-CN/7z2bhm2/6571059691/h/eRCozJPc0P6D8HNBb3qP94H1ForkIsaCTky_5R89ARk)
-[CPF banner](https://go.amazonsellerservices.com/e/229492/229-Wk13-mons-sel-locale-zh-CN/7z2bhm2/6571059691/h/eRCozJPc0P6D8HNBb3qP94H1ForkIsaCTky_5R89ARk)
-优先审核的 ASIN
-这些商品选自您的商品目录，可能是获得 Climate Pledge Friendly 认证的潜在候选。
-&lt;div style="padding: 0 20px; "&gt;&lt;table style="width:100%; border-collapse:collapse; text-align:center; font-family:Amazon Ember Display, Arial, sans-serif; border:2px solid #868D95; border-radius:10px 10px 0 0; overflow:hidden; "&gt;&lt;thead&gt;&lt;tr style="background-color:#dfdad5;"&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Dein Einkaufswagen wartet</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
-Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
- -7 % 21,81 € UVP: 23,49 €
-https://www.amazon.de/gp/product/B0DRCC2H56/?ref_=
-Einkaufswagen anzeigen
-https://www.amazon.de/gp/cart/view.html?ref_=cor
-Schaue dir weitere Optionen an
-Roaxkois Keramikmalset, Tassenmalset enthält Tassen, Pinsel, Farben und Anleitungen zum Bemalen, Keramik-Set für Zuhause, Bastelset für Erwachsene (Welle)
- 26,01 €
-https://www.amazon.de/gp/product/B0FLJ9RS6S/?ref_=ci_mcx_mr_2p_0_lm
-Roaxkois Keramik Bemalen Set - Kreatives Keramik Bastelset mit Farben, Pinseln und Anleitungen, Perfektes Tassen Bemalen Set für individuelle Geschenke und Freizeitgestaltung
- -11 % 20,97 € UVP: 23,49 €
-https://www.amazon.de/gp/product/B0FD8PWPNK/?ref_=ci_mcx_mr_2p_1_lm
-LEOSINYIN Keramik Bemalen Set, Tassen Bemalen Set, DIY Keramik Malset Kreatives Geschenk für Kinder &amp;amp; Erwachsene Enthält 2*Tassen, 2*Farbwanne, 4*Pinsel, 2 * 12 Farben und Anleitung
-Befristetes Angebot -37 % 18,99 € UVP: 29,99 €
-https://www.amazon.de/gp/product/B0FBXF765H/?re</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
- and eligibility</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>96
- Get ready to make this Prime Day your best yet.
- Hello,
- Get ready to make this Prime Day your best yet. We’ve made changes to promotion eligibility requirements to ensure deals deliver the value customers expect during our biggest shopping events like Prime Day. We’ve also simplified promotion fees to better align your costs and set FBA inbound dates to ensure your products are Prime-ready for the big event.
- Promotional eligibility
- To ensure deals offer substantial value to customers, and in turn drive higher engagement and more sales for you, Prime Exclusive price discounts and deals must now:
-- Be priced at or below the lowest sales price, including promotional prices from previous deals, coupons and price discounts, over the past 60 days .
-- Offer at least 5% off the lowest sales price, including promotional prices from previous deals, coupons and price discounts, over the past 30 days . We’re also giving you more time to act. The deal submission window will be open from March 24, 2026, through June 19, 2026. To schedule a deal, go to Create a new deal .
- For full eligibility details, go to Deals for events and Price discounts and events .
- You can use the Deals dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-09</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-04-09 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: X002A05YW5 Quantity: 2
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
- To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- CQhO1/+c38
- Unsellable Products:
-- FNSKU: X002C14R1B Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>[Action Required] – Update Inventory -FBA</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
-We recommend that you inbound additional inventory for your products immediately. To view the recommended replenishment quantity for these ASINs, go to “Restock inventory”:
-https://sellercentral.amazon.ca/restockinventory/recommendations
-Here is a sample of your high selling FBA ASINs, which are considered low in stock at the moment:
-B0DMFL5X12, B0D7QHCF8J
-You can download the full list of your ASIN at risk of out of stock at the following link:  https://www.sellercentral.amazon.ca/reportcentral/RestockReport/1
-For more information about Restock tool, you can visit this help page - https://sellercentral.amazon.ca/gp/help/G201634550
-If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
-If you are not the correct point of contact, please re-direct this report to the correct point of contact.
-If you wish to unsubscribe please REPLY ALL with the subject l</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -3904,21 +3917,69 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
+          <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Dein Einkaufswagen wartet</t>
+          <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
+ and eligibility</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Get ready to make this Prime Day your best yet.
+ Hello,
+ Get ready to make this Prime Day your best yet. We’ve made changes to promotion eligibility requirements to ensure deals deliver the value customers expect during our biggest shopping events like Prime Day. We’ve also simplified promotion fees to better align your costs and set FBA inbound dates to ensure your products are Prime-ready for the big event.
+ Promotional eligibility
+ To ensure deals offer substantial value to customers, and in turn drive higher engagement and more sales for you, Prime Exclusive price discounts and deals must now:
+- Be priced at or below the lowest sales price, including promotional prices from previous deals, coupons and price discounts, over the past 60 days .
+- Offer at least 5% off the lowest sales price, including promotional prices from previous deals, coupons and price discounts, over the past 30 days . We’re also giving you more time to act. The deal submission window will be open from March 24, 2026, through June 19, 2026. To schedule a deal, go to Create a new deal .
+ For full eligibility details, go to Deals for events and Price discounts and events .
+ You can use the Deals dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Dein Einkaufswagen wartet</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -3939,39 +4000,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -4004,39 +4065,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -4052,39 +4113,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4100,39 +4161,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4150,39 +4211,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4199,39 +4260,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -4255,39 +4316,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4302,39 +4363,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -4350,39 +4411,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4399,40 +4460,40 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -4448,39 +4509,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4500,39 +4561,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4548,40 +4609,40 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4597,39 +4658,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4646,39 +4707,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4697,39 +4758,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4747,39 +4808,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -4791,39 +4852,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4835,39 +4896,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -4879,39 +4940,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4923,39 +4984,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4967,39 +5028,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -5011,39 +5072,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5055,39 +5116,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5099,39 +5160,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -5149,39 +5210,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -5224,39 +5285,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5273,40 +5334,40 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5324,39 +5385,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5374,39 +5435,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5418,39 +5479,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5462,39 +5523,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5513,39 +5574,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5557,39 +5618,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5601,39 +5662,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5645,39 +5706,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5689,39 +5750,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5733,39 +5794,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5777,39 +5838,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5821,39 +5882,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5865,39 +5926,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5909,40 +5970,40 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5961,39 +6022,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6005,40 +6066,40 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -6050,39 +6111,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6094,39 +6155,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6145,39 +6206,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6189,39 +6250,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6240,39 +6301,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -6284,39 +6345,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6332,40 +6393,40 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6383,39 +6444,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6433,39 +6494,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -6481,39 +6542,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -6531,39 +6592,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -6604,39 +6665,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6654,40 +6715,40 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6705,39 +6766,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6754,39 +6815,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6804,39 +6865,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6854,39 +6915,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>最后机会：请在3月9日前提报春季促销日的促销</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>3月9日前提报春季促销日促销
 尊敬的卖家，
@@ -6901,39 +6962,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6947,39 +7008,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7000,39 +7061,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7056,39 +7117,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7111,39 +7172,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7166,39 +7227,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7220,39 +7281,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7275,39 +7336,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7330,39 +7391,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -7388,39 +7449,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7436,40 +7497,40 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7488,40 +7549,40 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7539,39 +7600,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -7585,39 +7646,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -7635,39 +7696,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -7684,39 +7745,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -7734,40 +7795,40 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -7786,39 +7847,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
@@ -7834,39 +7895,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>View your US Q1-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q1-2026
